--- a/data/trans_dic/P42-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P42-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38,24%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60,21%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,24%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,68; 48,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>53,42; 63,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,14; 64,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>29,59; 45,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,04; 47,8</t>
+          <t>38,68; 48,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,69; 63,2</t>
+          <t>53,42; 63,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,74; 64,5</t>
+          <t>55,14; 64,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 45,6</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>39,04; 47,8</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53,69; 63,2</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54,74; 64,5</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>30,16; 45,6</t>
+          <t>29,59; 45,96</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82,37%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88,08%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>82,37%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,15; 90,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,74; 94,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,63; 91,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>76,46; 90,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,22; 90,38</t>
+          <t>85,15; 90,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,67; 94,43</t>
+          <t>89,74; 94,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,52; 91,51</t>
+          <t>86,63; 91,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>76,56; 90,36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85,22; 90,38</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>89,67; 94,43</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86,52; 91,51</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,56; 90,36</t>
+          <t>76,46; 90,25</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93,17%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,5%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,96; 95,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96,89; 99,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>92,72; 96,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,67; 92,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,11; 95,14</t>
+          <t>90,96; 95,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>97,0; 99,02</t>
+          <t>96,89; 99,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,8; 96,11</t>
+          <t>92,72; 96,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,84; 92,84</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>91,11; 95,14</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97,0; 99,02</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92,8; 96,11</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>87,84; 92,84</t>
+          <t>87,67; 92,82</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>95,58%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89,68; 94,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,28; 96,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,17; 96,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,9; 97,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,83</t>
+          <t>89,68; 94,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,21; 96,77</t>
+          <t>93,28; 96,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,27; 96,81</t>
+          <t>93,17; 96,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,05; 97,01</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>90,09; 94,83</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>93,21; 96,77</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93,27; 96,81</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,05; 97,01</t>
+          <t>93,9; 97,04</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>93,44%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,34; 89,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,64; 96,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,83; 95,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,54; 95,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,61; 89,12</t>
+          <t>82,34; 89,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,42; 96,03</t>
+          <t>91,64; 96,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,01; 95,46</t>
+          <t>90,83; 95,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,25; 95,21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>82,61; 89,12</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>91,42; 96,03</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>91,01; 95,46</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,25; 95,21</t>
+          <t>91,54; 95,09</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>75,15%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84,25%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,54%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>70,17; 79,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>80,2; 87,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>83,5; 90,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,23; 93,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,34; 79,28</t>
+          <t>70,17; 79,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,52; 87,97</t>
+          <t>80,2; 87,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,44; 90,89</t>
+          <t>83,5; 90,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,88; 93,13</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>70,34; 79,28</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>80,52; 87,97</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>83,44; 90,89</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>21,88; 93,13</t>
+          <t>21,23; 93,08</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>82,84%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>72,42%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,07; 62,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67,72; 76,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>72,34; 81,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>79,95; 85,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,09; 62,89</t>
+          <t>51,07; 62,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,84; 77,0</t>
+          <t>67,72; 76,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,67; 81,37</t>
+          <t>72,34; 81,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,47; 85,22</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>52,09; 62,89</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>67,84; 77,0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>71,67; 81,37</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>79,47; 85,22</t>
+          <t>79,95; 85,5</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>78,55%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>78,55%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,74; 80,45</t>
+          <t>77,58; 80,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,08; 88,28</t>
+          <t>85,99; 88,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,12; 88,42</t>
+          <t>85,98; 88,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59,58; 85,19</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>77,74; 80,45</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>86,08; 88,28</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>86,12; 88,42</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>59,58; 85,19</t>
+          <t>60,88; 85,34</t>
         </is>
       </c>
     </row>
@@ -1764,17 +1408,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
@@ -1788,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1801,22 +1444,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido alguna vez al ginecólogo</t>
+          <t>Población que ha acudido alguna vez al ginecólogo (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1824,20 +1463,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1878,26 +1509,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1914,10 +1525,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1932,22 +1539,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1966,26 +1573,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
@@ -2000,22 +1587,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203329</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2034,26 +1621,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99543</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>203329</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>250354</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>235063</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99543</t>
         </is>
@@ -2068,62 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>180505; 223999</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>228725; 271079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>215274; 251868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>77020; 119649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>182157; 223046</t>
+          <t>180505; 223999</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>229898; 270621</t>
+          <t>228725; 271079</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>213723; 251824</t>
+          <t>215274; 251868</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78515; 118696</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>182157; 223046</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>229898; 270621</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>213723; 251824</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>78515; 118696</t>
+          <t>77020; 119649</t>
         </is>
       </c>
     </row>
@@ -2140,22 +1687,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>518</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>522</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2174,26 +1721,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>263</t>
         </is>
@@ -2208,22 +1735,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>549155</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>557326</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>499170</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2242,26 +1769,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>324080</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>549155</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>557326</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>499170</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>324080</t>
         </is>
@@ -2276,62 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>530872; 564558</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>541648; 568942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>485136; 512310</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>300832; 355087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>531341; 563513</t>
+          <t>530872; 564558</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>541212; 569921</t>
+          <t>541648; 568942</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>484550; 512472</t>
+          <t>485136; 512310</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>301226; 355520</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>531341; 563513</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>541212; 569921</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>484550; 512472</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>301226; 355520</t>
+          <t>300832; 355087</t>
         </is>
       </c>
     </row>
@@ -2348,22 +1835,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2382,26 +1869,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>520</t>
         </is>
@@ -2416,22 +1883,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>641702</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>696007</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>621719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>335665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2450,26 +1917,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>335665</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>641702</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>696007</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>621719</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>335665</t>
         </is>
@@ -2484,62 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>626484; 654290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>686804; 702198</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>609170; 631457</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>325163; 344260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>627483; 655245</t>
+          <t>626484; 654290</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>687572; 701907</t>
+          <t>686804; 702198</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>609750; 631503</t>
+          <t>609170; 631457</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>325799; 344334</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>627483; 655245</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>687572; 701907</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>609750; 631503</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>325799; 344334</t>
+          <t>325163; 344260</t>
         </is>
       </c>
     </row>
@@ -2556,22 +1983,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>466</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2590,26 +2017,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>750</t>
         </is>
@@ -2624,22 +2031,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477701</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>583993</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>613499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>483122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2658,26 +2065,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>483122</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>477701</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>583993</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>613499</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>483122</t>
         </is>
@@ -2692,62 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>462432; 487924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>571821; 593583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>599893; 622726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>474651; 490526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>464540; 488966</t>
+          <t>462432; 487924</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>571355; 593192</t>
+          <t>571821; 593583</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>600556; 623328</t>
+          <t>599893; 622726</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>475380; 490335</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>464540; 488966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571355; 593192</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>600556; 623328</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>475380; 490335</t>
+          <t>474651; 490526</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2131,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>339</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>380</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2798,26 +2165,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
@@ -2832,22 +2179,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>347172</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>420342</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>461391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2866,26 +2213,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>375423</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347172</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>420342</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>461391</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>375423</t>
         </is>
@@ -2900,62 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>331826; 360614</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>409412; 429971</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>448286; 471441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>367806; 382039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>332885; 359139</t>
+          <t>331826; 360614</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>408418; 429022</t>
+          <t>409412; 429971</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>449206; 471134</t>
+          <t>448286; 471441</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>366612; 382534</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>332885; 359139</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>408418; 429022</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>449206; 471134</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>366612; 382534</t>
+          <t>367806; 382039</t>
         </is>
       </c>
     </row>
@@ -2972,22 +2279,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>277</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3006,26 +2313,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
@@ -3040,22 +2327,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257031</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295821</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298114</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3074,26 +2361,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>298114</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>257031</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>295821</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>328777</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>298114</t>
         </is>
@@ -3108,62 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>240000; 270401</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>281575; 308136</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>313609; 339545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>111926; 490763</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>240591; 271174</t>
+          <t>240000; 270401</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>282718; 308879</t>
+          <t>281575; 308136</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>313368; 341352</t>
+          <t>313609; 339545</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>115350; 491016</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>240591; 271174</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>282718; 308879</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>313368; 341352</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>115350; 491016</t>
+          <t>111926; 490763</t>
         </is>
       </c>
     </row>
@@ -3180,22 +2427,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3214,26 +2461,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
@@ -3248,22 +2475,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185265</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>306934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3282,26 +2509,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>304168</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>185265</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>279359</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>306934</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>304168</t>
         </is>
@@ -3316,62 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>165783; 203981</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>261212; 296478</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>286884; 323804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>293554; 313920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>169112; 204174</t>
+          <t>165783; 203981</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>261709; 297044</t>
+          <t>261212; 296478</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>284261; 322725</t>
+          <t>286884; 323804</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>291797; 312895</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>169112; 204174</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>261709; 297044</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>284261; 322725</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>291797; 312895</t>
+          <t>293554; 313920</t>
         </is>
       </c>
     </row>
@@ -3388,22 +2575,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3422,26 +2609,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>3520</t>
         </is>
@@ -3456,22 +2623,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3083200</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3066554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2220114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3490,26 +2657,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2220114</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2661356</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3083200</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3066554</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2220114</t>
         </is>
@@ -3524,62 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2615119; 2706419</t>
+          <t>2609848; 2707448</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3044776; 3122790</t>
+          <t>3041580; 3124401</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3028943; 3109819</t>
+          <t>3023913; 3102832</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1683901; 2407647</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>2615119; 2706419</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>3044776; 3122790</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>3028943; 3109819</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1683901; 2407647</t>
+          <t>1720767; 2411873</t>
         </is>
       </c>
     </row>
@@ -3591,17 +2718,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P42-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P42-Edad-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 48,0</t>
+          <t>38,82; 47,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,42; 63,31</t>
+          <t>53,74; 63,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,14; 64,51</t>
+          <t>55,04; 64,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,59; 45,96</t>
+          <t>31,33; 46,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,68; 48,0</t>
+          <t>38,82; 47,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,42; 63,31</t>
+          <t>53,74; 63,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,14; 64,51</t>
+          <t>55,04; 64,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,59; 45,96</t>
+          <t>31,33; 46,32</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,15; 90,55</t>
+          <t>85,25; 90,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,74; 94,27</t>
+          <t>89,86; 94,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,63; 91,48</t>
+          <t>86,22; 91,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,46; 90,25</t>
+          <t>73,25; 82,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,15; 90,55</t>
+          <t>85,25; 90,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,74; 94,27</t>
+          <t>89,86; 94,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,63; 91,48</t>
+          <t>86,22; 91,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>76,46; 90,25</t>
+          <t>73,25; 82,31</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,96; 95,0</t>
+          <t>91,1; 95,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,89; 99,06</t>
+          <t>96,8; 99,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,72; 96,11</t>
+          <t>92,75; 96,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,67; 92,82</t>
+          <t>87,17; 92,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,96; 95,0</t>
+          <t>91,1; 95,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96,89; 99,06</t>
+          <t>96,8; 99,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,72; 96,11</t>
+          <t>92,75; 96,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,67; 92,82</t>
+          <t>87,17; 92,36</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,68; 94,62</t>
+          <t>89,87; 94,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,83</t>
+          <t>93,27; 96,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,17; 96,71</t>
+          <t>93,4; 96,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,9; 97,04</t>
+          <t>93,22; 96,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,68; 94,62</t>
+          <t>89,87; 94,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 96,83</t>
+          <t>93,27; 96,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,17; 96,71</t>
+          <t>93,4; 96,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,9; 97,04</t>
+          <t>93,22; 96,37</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,34; 89,49</t>
+          <t>82,39; 89,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>91,64; 96,24</t>
+          <t>91,51; 95,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,83; 95,52</t>
+          <t>90,89; 95,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,54; 95,09</t>
+          <t>91,17; 94,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,34; 89,49</t>
+          <t>82,39; 89,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,64; 96,24</t>
+          <t>91,51; 95,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,83; 95,52</t>
+          <t>90,89; 95,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,54; 95,09</t>
+          <t>91,17; 94,75</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,17; 79,06</t>
+          <t>70,93; 79,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,2; 87,76</t>
+          <t>80,18; 88,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,5; 90,41</t>
+          <t>83,59; 90,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 93,08</t>
+          <t>90,33; 94,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,17; 79,06</t>
+          <t>70,93; 79,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,2; 87,76</t>
+          <t>80,18; 88,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83,5; 90,41</t>
+          <t>83,59; 90,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 93,08</t>
+          <t>90,33; 94,26</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>51,07; 62,84</t>
+          <t>51,49; 62,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,72; 76,86</t>
+          <t>67,46; 76,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,34; 81,64</t>
+          <t>71,98; 82,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79,95; 85,5</t>
+          <t>79,82; 85,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,07; 62,84</t>
+          <t>51,49; 62,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,72; 76,86</t>
+          <t>67,46; 76,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,34; 81,64</t>
+          <t>71,98; 82,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79,95; 85,5</t>
+          <t>79,82; 85,56</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,58; 80,48</t>
+          <t>77,69; 80,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,99; 88,33</t>
+          <t>85,92; 88,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,98; 88,22</t>
+          <t>85,98; 88,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,88; 85,34</t>
+          <t>82,19; 85,06</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>115572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>115572</t>
         </is>
       </c>
     </row>
@@ -1635,42 +1635,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>180505; 223999</t>
+          <t>181135; 222577</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228725; 271079</t>
+          <t>230100; 271207</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215274; 251868</t>
+          <t>214898; 251980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77020; 119649</t>
+          <t>93537; 138274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>180505; 223999</t>
+          <t>181135; 222577</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>228725; 271079</t>
+          <t>230100; 271207</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>215274; 251868</t>
+          <t>214898; 251980</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>77020; 119649</t>
+          <t>93537; 138274</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324080</t>
+          <t>287860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>324080</t>
+          <t>287860</t>
         </is>
       </c>
     </row>
@@ -1783,42 +1783,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>530872; 564558</t>
+          <t>531503; 564499</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>541648; 568942</t>
+          <t>542348; 569558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>485136; 512310</t>
+          <t>482876; 511536</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300832; 355087</t>
+          <t>269086; 302365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>530872; 564558</t>
+          <t>531503; 564499</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>541648; 568942</t>
+          <t>542348; 569558</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>485136; 512310</t>
+          <t>482876; 511536</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>300832; 355087</t>
+          <t>269086; 302365</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>335665</t>
+          <t>382537</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>335665</t>
+          <t>382537</t>
         </is>
       </c>
     </row>
@@ -1931,42 +1931,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>626484; 654290</t>
+          <t>627402; 654351</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686804; 702198</t>
+          <t>686185; 702119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>609170; 631457</t>
+          <t>609387; 632555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325163; 344260</t>
+          <t>370458; 392517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>626484; 654290</t>
+          <t>627402; 654351</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>686804; 702198</t>
+          <t>686185; 702119</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>609170; 631457</t>
+          <t>609387; 632555</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>325163; 344260</t>
+          <t>370458; 392517</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483122</t>
+          <t>486462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>483122</t>
+          <t>486462</t>
         </is>
       </c>
     </row>
@@ -2079,42 +2079,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>462432; 487924</t>
+          <t>463409; 488496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>571821; 593583</t>
+          <t>571730; 593109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>599893; 622726</t>
+          <t>601353; 623588</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>474651; 490526</t>
+          <t>477705; 493850</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>462432; 487924</t>
+          <t>463409; 488496</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>571821; 593583</t>
+          <t>571730; 593109</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>599893; 622726</t>
+          <t>601353; 623588</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>474651; 490526</t>
+          <t>477705; 493850</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375423</t>
+          <t>416517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>375423</t>
+          <t>416517</t>
         </is>
       </c>
     </row>
@@ -2227,42 +2227,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>331826; 360614</t>
+          <t>332026; 359792</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>409412; 429971</t>
+          <t>408845; 428835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>448286; 471441</t>
+          <t>448586; 471776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>367806; 382039</t>
+          <t>407897; 423951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>331826; 360614</t>
+          <t>332026; 359792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>409412; 429971</t>
+          <t>408845; 428835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>448286; 471441</t>
+          <t>448586; 471776</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>367806; 382039</t>
+          <t>407897; 423951</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298114</t>
+          <t>323253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>298114</t>
+          <t>323253</t>
         </is>
       </c>
     </row>
@@ -2375,42 +2375,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>240000; 270401</t>
+          <t>242595; 270577</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>281575; 308136</t>
+          <t>281502; 309122</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>313609; 339545</t>
+          <t>313926; 340254</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111926; 490763</t>
+          <t>315830; 329557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>240000; 270401</t>
+          <t>242595; 270577</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>281575; 308136</t>
+          <t>281502; 309122</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>313609; 339545</t>
+          <t>313926; 340254</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>111926; 490763</t>
+          <t>315830; 329557</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>331574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>304168</t>
+          <t>331574</t>
         </is>
       </c>
     </row>
@@ -2523,42 +2523,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>165783; 203981</t>
+          <t>167147; 204107</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>261212; 296478</t>
+          <t>260212; 296699</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>286884; 323804</t>
+          <t>285462; 325275</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293554; 313920</t>
+          <t>318830; 341766</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>165783; 203981</t>
+          <t>167147; 204107</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>261212; 296478</t>
+          <t>260212; 296699</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>286884; 323804</t>
+          <t>285462; 325275</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>293554; 313920</t>
+          <t>318830; 341766</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2220114</t>
+          <t>2343774</t>
         </is>
       </c>
     </row>
@@ -2671,42 +2671,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2609848; 2707448</t>
+          <t>2613736; 2708203</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3041580; 3124401</t>
+          <t>3039240; 3120170</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3023913; 3102832</t>
+          <t>3023962; 3105291</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1720767; 2411873</t>
+          <t>2301184; 2381376</t>
         </is>
       </c>
     </row>
